--- a/data/forecasts/cogs-nov-2025-forecast.xlsx
+++ b/data/forecasts/cogs-nov-2025-forecast.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dan.jellesma/python/costvsforecast/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dan.jellesma/python/streamdeck/data/forecasts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F364F7E-5BF6-7D4F-99BB-907B46ABF885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF33B6B8-5AA6-F843-B877-B8B6EB8FE0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3620" yWindow="4920" windowWidth="26440" windowHeight="15440" xr2:uid="{6B9648A2-E53C-D049-BDC7-92F9AFC8A135}"/>
+    <workbookView xWindow="14040" yWindow="4320" windowWidth="26440" windowHeight="19740" xr2:uid="{6B9648A2-E53C-D049-BDC7-92F9AFC8A135}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
     <t>ads</t>
   </si>
@@ -177,16 +177,58 @@
   </si>
   <si>
     <t>Apr-2026</t>
+  </si>
+  <si>
+    <t>Jan-2027</t>
+  </si>
+  <si>
+    <t>Feb-2027</t>
+  </si>
+  <si>
+    <t>Mar-2027</t>
+  </si>
+  <si>
+    <t>Apr-2027</t>
+  </si>
+  <si>
+    <t>May-2026</t>
+  </si>
+  <si>
+    <t>Jun-2026</t>
+  </si>
+  <si>
+    <t>Jul-2026</t>
+  </si>
+  <si>
+    <t>Aug-2026</t>
+  </si>
+  <si>
+    <t>Sep-2026</t>
+  </si>
+  <si>
+    <t>Oct-2026</t>
+  </si>
+  <si>
+    <t>Nov-2026</t>
+  </si>
+  <si>
+    <t>Dec-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -548,10 +590,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38213635-96FF-8A49-9052-7F5A74D345D0}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -576,8 +618,44 @@
       <c r="H1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -602,8 +680,44 @@
       <c r="H2">
         <v>69118.380106521028</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <v>86691.562934308196</v>
+      </c>
+      <c r="J2">
+        <v>86004.979255146391</v>
+      </c>
+      <c r="K2">
+        <v>92192.863349287785</v>
+      </c>
+      <c r="L2">
+        <v>93954.791982780676</v>
+      </c>
+      <c r="M2">
+        <v>93217.103131556592</v>
+      </c>
+      <c r="N2">
+        <v>98501.583301634571</v>
+      </c>
+      <c r="O2">
+        <v>98728.966904500863</v>
+      </c>
+      <c r="P2">
+        <v>102079.46512599742</v>
+      </c>
+      <c r="Q2">
+        <v>106880.25977725739</v>
+      </c>
+      <c r="R2">
+        <v>101783.66924196256</v>
+      </c>
+      <c r="S2">
+        <v>114505.95299878025</v>
+      </c>
+      <c r="T2">
+        <v>114642.91535042072</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -628,8 +742,44 @@
       <c r="H3">
         <v>388142.15373400185</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <v>399173.68534363323</v>
+      </c>
+      <c r="J3">
+        <v>390160.08599716419</v>
+      </c>
+      <c r="K3">
+        <v>407197.07641904021</v>
+      </c>
+      <c r="L3">
+        <v>411269.04718323075</v>
+      </c>
+      <c r="M3">
+        <v>401982.32676296425</v>
+      </c>
+      <c r="N3">
+        <v>419535.55503161374</v>
+      </c>
+      <c r="O3">
+        <v>410062.17153089977</v>
+      </c>
+      <c r="P3">
+        <v>427968.21968774911</v>
+      </c>
+      <c r="Q3">
+        <v>432247.9018846266</v>
+      </c>
+      <c r="R3">
+        <v>394321.63436442713</v>
+      </c>
+      <c r="S3">
+        <v>440936.08471250749</v>
+      </c>
+      <c r="T3">
+        <v>430979.46344480588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -654,8 +804,44 @@
       <c r="H4">
         <v>485959.63474697067</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>535775.76777146885</v>
+      </c>
+      <c r="J4">
+        <v>523677.60527340346</v>
+      </c>
+      <c r="K4">
+        <v>546544.86070367531</v>
+      </c>
+      <c r="L4">
+        <v>552010.30931071215</v>
+      </c>
+      <c r="M4">
+        <v>539545.5603907929</v>
+      </c>
+      <c r="N4">
+        <v>563105.71652785758</v>
+      </c>
+      <c r="O4">
+        <v>550390.42615464772</v>
+      </c>
+      <c r="P4">
+        <v>574424.14143006736</v>
+      </c>
+      <c r="Q4">
+        <v>580168.38284436811</v>
+      </c>
+      <c r="R4">
+        <v>529263.28602705582</v>
+      </c>
+      <c r="S4">
+        <v>591829.76733953983</v>
+      </c>
+      <c r="T4">
+        <v>578465.86936735676</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -680,8 +866,44 @@
       <c r="H5">
         <v>15211.490207211069</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>15113.38826449222</v>
+      </c>
+      <c r="J5">
+        <v>14772.118206906915</v>
+      </c>
+      <c r="K5">
+        <v>15417.167368608511</v>
+      </c>
+      <c r="L5">
+        <v>15571.339042294601</v>
+      </c>
+      <c r="M5">
+        <v>15219.728160694402</v>
+      </c>
+      <c r="N5">
+        <v>15884.322957044724</v>
+      </c>
+      <c r="O5">
+        <v>15525.644696724357</v>
+      </c>
+      <c r="P5">
+        <v>16203.59784848132</v>
+      </c>
+      <c r="Q5">
+        <v>16365.633826966134</v>
+      </c>
+      <c r="R5">
+        <v>14929.681439567816</v>
+      </c>
+      <c r="S5">
+        <v>16694.58306688815</v>
+      </c>
+      <c r="T5">
+        <v>16317.60861053907</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -706,8 +928,44 @@
       <c r="H6">
         <v>125616.73205634611</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <v>20475.18416305026</v>
+      </c>
+      <c r="J6">
+        <v>20012.841294852355</v>
+      </c>
+      <c r="K6">
+        <v>20886.73536472757</v>
+      </c>
+      <c r="L6">
+        <v>21095.602718374852</v>
+      </c>
+      <c r="M6">
+        <v>20619.250398927677</v>
+      </c>
+      <c r="N6">
+        <v>21519.624333014188</v>
+      </c>
+      <c r="O6">
+        <v>21033.697331946121</v>
+      </c>
+      <c r="P6">
+        <v>21952.168782107768</v>
+      </c>
+      <c r="Q6">
+        <v>22171.690469928846</v>
+      </c>
+      <c r="R6">
+        <v>20226.303435147995</v>
+      </c>
+      <c r="S6">
+        <v>22617.341448374413</v>
+      </c>
+      <c r="T6">
+        <v>22106.627286636933</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -732,8 +990,44 @@
       <c r="H7">
         <v>69909.214640863225</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>71598.723754216684</v>
+      </c>
+      <c r="J7">
+        <v>69981.978379121487</v>
+      </c>
+      <c r="K7">
+        <v>73037.858101676422</v>
+      </c>
+      <c r="L7">
+        <v>73768.236682693212</v>
+      </c>
+      <c r="M7">
+        <v>72102.502305987247</v>
+      </c>
+      <c r="N7">
+        <v>75250.978240015349</v>
+      </c>
+      <c r="O7">
+        <v>73551.762602337578</v>
+      </c>
+      <c r="P7">
+        <v>76763.522902639656</v>
+      </c>
+      <c r="Q7">
+        <v>77531.158131666045</v>
+      </c>
+      <c r="R7">
+        <v>70728.424256887607</v>
+      </c>
+      <c r="S7">
+        <v>79089.534410112523</v>
+      </c>
+      <c r="T7">
+        <v>77303.641697626139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -758,8 +1052,44 @@
       <c r="H8">
         <v>181961.88457839066</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8">
+        <v>207307.73461280478</v>
+      </c>
+      <c r="J8">
+        <v>200620.38833497235</v>
+      </c>
+      <c r="K8">
+        <v>207307.73461280478</v>
+      </c>
+      <c r="L8">
+        <v>40000</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -784,8 +1114,44 @@
       <c r="H9">
         <v>15675.887142274103</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>11175.645858732647</v>
+      </c>
+      <c r="J9">
+        <v>10923.292565148362</v>
+      </c>
+      <c r="K9">
+        <v>11400.276340493172</v>
+      </c>
+      <c r="L9">
+        <v>11514.279103898107</v>
+      </c>
+      <c r="M9">
+        <v>11254.279253164923</v>
+      </c>
+      <c r="N9">
+        <v>11745.716113886459</v>
+      </c>
+      <c r="O9">
+        <v>11480.490266153536</v>
+      </c>
+      <c r="P9">
+        <v>11981.805007775576</v>
+      </c>
+      <c r="Q9">
+        <v>12101.623057853332</v>
+      </c>
+      <c r="R9">
+        <v>11039.80322826104</v>
+      </c>
+      <c r="S9">
+        <v>12344.865681316182</v>
+      </c>
+      <c r="T9">
+        <v>12066.110649802593</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -810,8 +1176,44 @@
       <c r="H10">
         <v>395774.48154298379</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <v>381575.55317063996</v>
+      </c>
+      <c r="J10">
+        <v>372959.33100227074</v>
+      </c>
+      <c r="K10">
+        <v>389245.22178936977</v>
+      </c>
+      <c r="L10">
+        <v>393137.67400726362</v>
+      </c>
+      <c r="M10">
+        <v>384260.37169097055</v>
+      </c>
+      <c r="N10">
+        <v>401039.74125480966</v>
+      </c>
+      <c r="O10">
+        <v>391984.00516195898</v>
+      </c>
+      <c r="P10">
+        <v>409100.64005403122</v>
+      </c>
+      <c r="Q10">
+        <v>413191.64645457157</v>
+      </c>
+      <c r="R10">
+        <v>376937.4116688802</v>
+      </c>
+      <c r="S10">
+        <v>421496.79854830838</v>
+      </c>
+      <c r="T10">
+        <v>411979.12890366931</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -836,8 +1238,44 @@
       <c r="H11">
         <v>8820.3477349408968</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11">
+        <v>9050.5763574124885</v>
+      </c>
+      <c r="J11">
+        <v>8846.2085041805949</v>
+      </c>
+      <c r="K11">
+        <v>9232.4929421964771</v>
+      </c>
+      <c r="L11">
+        <v>9324.8178716184448</v>
+      </c>
+      <c r="M11">
+        <v>9114.2574680657708</v>
+      </c>
+      <c r="N11">
+        <v>9512.2467108379769</v>
+      </c>
+      <c r="O11">
+        <v>9297.4540431738915</v>
+      </c>
+      <c r="P11">
+        <v>9703.442869725819</v>
+      </c>
+      <c r="Q11">
+        <v>9800.4772984230767</v>
+      </c>
+      <c r="R11">
+        <v>8940.5644515936983</v>
+      </c>
+      <c r="S11">
+        <v>9997.4668921213797</v>
+      </c>
+      <c r="T11">
+        <v>9771.7176397186413</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -862,8 +1300,44 @@
       <c r="H12">
         <v>143729.32282990805</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12">
+        <v>129179.50111926981</v>
+      </c>
+      <c r="J12">
+        <v>126262.5446423831</v>
+      </c>
+      <c r="K12">
+        <v>151776.00909176713</v>
+      </c>
+      <c r="L12">
+        <v>153293.76918268483</v>
+      </c>
+      <c r="M12">
+        <v>149832.29697533388</v>
+      </c>
+      <c r="N12">
+        <v>156374.97394325683</v>
+      </c>
+      <c r="O12">
+        <v>152843.92614453813</v>
+      </c>
+      <c r="P12">
+        <v>159518.1109195163</v>
+      </c>
+      <c r="Q12">
+        <v>161113.29202871147</v>
+      </c>
+      <c r="R12">
+        <v>146976.89995393419</v>
+      </c>
+      <c r="S12">
+        <v>164351.66919848855</v>
+      </c>
+      <c r="T12">
+        <v>160640.50247465173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -888,8 +1362,44 @@
       <c r="H13">
         <v>209520.72393100467</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13">
+        <v>186381.84655063378</v>
+      </c>
+      <c r="J13">
+        <v>182173.22420916788</v>
+      </c>
+      <c r="K13">
+        <v>130128.12166630151</v>
+      </c>
+      <c r="L13">
+        <v>132029.40288296455</v>
+      </c>
+      <c r="M13">
+        <v>127693.25507592989</v>
+      </c>
+      <c r="N13">
+        <v>135889.19388091218</v>
+      </c>
+      <c r="O13">
+        <v>131465.88950295607</v>
+      </c>
+      <c r="P13">
+        <v>139826.56667791848</v>
+      </c>
+      <c r="Q13">
+        <v>141824.83234469767</v>
+      </c>
+      <c r="R13">
+        <v>124116.33092606615</v>
+      </c>
+      <c r="S13">
+        <v>145881.51147482605</v>
+      </c>
+      <c r="T13">
+        <v>141232.57411894295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -914,8 +1424,44 @@
       <c r="H14">
         <v>14127.116595534551</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14">
+        <v>11838.698821203627</v>
+      </c>
+      <c r="J14">
+        <v>11571.373363950643</v>
+      </c>
+      <c r="K14">
+        <v>12076.656667509818</v>
+      </c>
+      <c r="L14">
+        <v>12197.42323418492</v>
+      </c>
+      <c r="M14">
+        <v>11921.997548251711</v>
+      </c>
+      <c r="N14">
+        <v>12442.591441192038</v>
+      </c>
+      <c r="O14">
+        <v>12161.629698971568</v>
+      </c>
+      <c r="P14">
+        <v>12692.687529159995</v>
+      </c>
+      <c r="Q14">
+        <v>12819.614404451597</v>
+      </c>
+      <c r="R14">
+        <v>11694.796624448103</v>
+      </c>
+      <c r="S14">
+        <v>13077.288653981072</v>
+      </c>
+      <c r="T14">
+        <v>12781.995039213758</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -940,8 +1486,44 @@
       <c r="H15">
         <v>2791.0205605368687</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15">
+        <v>60.484877661790634</v>
+      </c>
+      <c r="J15">
+        <v>59.119090101685693</v>
+      </c>
+      <c r="K15">
+        <v>61.700623702792619</v>
+      </c>
+      <c r="L15">
+        <v>62.317629939820563</v>
+      </c>
+      <c r="M15">
+        <v>60.910457650856877</v>
+      </c>
+      <c r="N15">
+        <v>63.57021430161096</v>
+      </c>
+      <c r="O15">
+        <v>62.134757849639087</v>
+      </c>
+      <c r="P15">
+        <v>64.84797560907333</v>
+      </c>
+      <c r="Q15">
+        <v>65.496455365164067</v>
+      </c>
+      <c r="R15">
+        <v>59.749669604091615</v>
+      </c>
+      <c r="S15">
+        <v>66.812934118003852</v>
+      </c>
+      <c r="T15">
+        <v>65.304254960500558</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -966,8 +1548,44 @@
       <c r="H16">
         <v>22833.612325843926</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16">
+        <v>22140.25790806278</v>
+      </c>
+      <c r="J16">
+        <v>21640.31660046137</v>
+      </c>
+      <c r="K16">
+        <v>22585.277092014843</v>
+      </c>
+      <c r="L16">
+        <v>22811.129862934995</v>
+      </c>
+      <c r="M16">
+        <v>22296.039833771953</v>
+      </c>
+      <c r="N16">
+        <v>23269.633573179992</v>
+      </c>
+      <c r="O16">
+        <v>22744.190234430764</v>
+      </c>
+      <c r="P16">
+        <v>23737.353208000906</v>
+      </c>
+      <c r="Q16">
+        <v>23974.726740080914</v>
+      </c>
+      <c r="R16">
+        <v>21871.137813209305</v>
+      </c>
+      <c r="S16">
+        <v>24456.618747556538</v>
+      </c>
+      <c r="T16">
+        <v>23904.372517773012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -992,8 +1610,44 @@
       <c r="H17">
         <v>199743.06418971645</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17">
+        <v>203744.36929636722</v>
+      </c>
+      <c r="J17">
+        <v>199143.68998967513</v>
+      </c>
+      <c r="K17">
+        <v>207839.63111922418</v>
+      </c>
+      <c r="L17">
+        <v>209918.02743041649</v>
+      </c>
+      <c r="M17">
+        <v>205177.94294005228</v>
+      </c>
+      <c r="N17">
+        <v>214137.37978176787</v>
+      </c>
+      <c r="O17">
+        <v>209302.0195931473</v>
+      </c>
+      <c r="P17">
+        <v>218441.54111538138</v>
+      </c>
+      <c r="Q17">
+        <v>220625.95652653518</v>
+      </c>
+      <c r="R17">
+        <v>201267.80808291666</v>
+      </c>
+      <c r="S17">
+        <v>225060.53825271851</v>
+      </c>
+      <c r="T17">
+        <v>219978.52609862495</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1018,8 +1672,44 @@
       <c r="H18">
         <v>27551.409427523835</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18">
+        <v>26705.120744123349</v>
+      </c>
+      <c r="J18">
+        <v>26102.10188861089</v>
+      </c>
+      <c r="K18">
+        <v>27241.893671080226</v>
+      </c>
+      <c r="L18">
+        <v>27514.312607791035</v>
+      </c>
+      <c r="M18">
+        <v>26893.021677937693</v>
+      </c>
+      <c r="N18">
+        <v>28067.35029120764</v>
+      </c>
+      <c r="O18">
+        <v>27433.571413664235</v>
+      </c>
+      <c r="P18">
+        <v>28631.504032060908</v>
+      </c>
+      <c r="Q18">
+        <v>28917.819072381517</v>
+      </c>
+      <c r="R18">
+        <v>26380.51365699837</v>
+      </c>
+      <c r="S18">
+        <v>29499.06723573638</v>
+      </c>
+      <c r="T18">
+        <v>28832.959265897181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1044,8 +1734,44 @@
       <c r="H19">
         <v>36906.141406232848</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <v>37424.651513477984</v>
+      </c>
+      <c r="J19">
+        <v>36579.578737367206</v>
+      </c>
+      <c r="K19">
+        <v>38176.887008898892</v>
+      </c>
+      <c r="L19">
+        <v>38558.655878987891</v>
+      </c>
+      <c r="M19">
+        <v>37687.976552688167</v>
+      </c>
+      <c r="N19">
+        <v>39333.684862155547</v>
+      </c>
+      <c r="O19">
+        <v>38445.504881397195</v>
+      </c>
+      <c r="P19">
+        <v>40124.291927884871</v>
+      </c>
+      <c r="Q19">
+        <v>40525.534847163719</v>
+      </c>
+      <c r="R19">
+        <v>36969.74598315452</v>
+      </c>
+      <c r="S19">
+        <v>41340.098097591705</v>
+      </c>
+      <c r="T19">
+        <v>40406.612011517071</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1070,8 +1796,44 @@
       <c r="H20">
         <v>9845.0233814609473</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20">
+        <v>11159.297022042607</v>
+      </c>
+      <c r="J20">
+        <v>10907.312895738422</v>
+      </c>
+      <c r="K20">
+        <v>11383.598892185662</v>
+      </c>
+      <c r="L20">
+        <v>11497.434881107522</v>
+      </c>
+      <c r="M20">
+        <v>11237.815383792191</v>
+      </c>
+      <c r="N20">
+        <v>11728.533322217785</v>
+      </c>
+      <c r="O20">
+        <v>11463.695473006412</v>
+      </c>
+      <c r="P20">
+        <v>11964.27684199436</v>
+      </c>
+      <c r="Q20">
+        <v>12083.919610414303</v>
+      </c>
+      <c r="R20">
+        <v>11023.65311556505</v>
+      </c>
+      <c r="S20">
+        <v>12326.806394583629</v>
+      </c>
+      <c r="T20">
+        <v>12048.459153415615</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -1096,8 +1858,44 @@
       <c r="H21">
         <v>1245.0333838925089</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21">
+        <v>60303.004126228159</v>
+      </c>
+      <c r="J21">
+        <v>58941.323387893986</v>
+      </c>
+      <c r="K21">
+        <v>61515.094509165341</v>
+      </c>
+      <c r="L21">
+        <v>62130.245454257012</v>
+      </c>
+      <c r="M21">
+        <v>60727.304427870571</v>
+      </c>
+      <c r="N21">
+        <v>63379.063387887581</v>
+      </c>
+      <c r="O21">
+        <v>61947.923246870756</v>
+      </c>
+      <c r="P21">
+        <v>64652.982561984114</v>
+      </c>
+      <c r="Q21">
+        <v>65299.512387603958</v>
+      </c>
+      <c r="R21">
+        <v>59570.006784562582</v>
+      </c>
+      <c r="S21">
+        <v>66612.032586594782</v>
+      </c>
+      <c r="T21">
+        <v>65107.889915284599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1122,8 +1920,44 @@
       <c r="H22">
         <v>141029.94815193175</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <v>179219.5782851947</v>
+      </c>
+      <c r="J22">
+        <v>175172.68458198066</v>
+      </c>
+      <c r="K22">
+        <v>91410.945904363543</v>
+      </c>
+      <c r="L22">
+        <v>92325.055363407184</v>
+      </c>
+      <c r="M22">
+        <v>90240.296048749602</v>
+      </c>
+      <c r="N22">
+        <v>94180.788976211654</v>
+      </c>
+      <c r="O22">
+        <v>92054.125999329452</v>
+      </c>
+      <c r="P22">
+        <v>96073.822834633509</v>
+      </c>
+      <c r="Q22">
+        <v>97034.561062979847</v>
+      </c>
+      <c r="R22">
+        <v>88520.560866486121</v>
+      </c>
+      <c r="S22">
+        <v>98984.955740345744</v>
+      </c>
+      <c r="T22">
+        <v>96749.811578466964</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -1148,8 +1982,44 @@
       <c r="H23">
         <v>846150.0376547568</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23">
+        <v>725330.09912100271</v>
+      </c>
+      <c r="J23">
+        <v>698514.2378288703</v>
+      </c>
+      <c r="K23">
+        <v>718707.71351148165</v>
+      </c>
+      <c r="L23">
+        <v>720566.390784421</v>
+      </c>
+      <c r="M23">
+        <v>698828.13183777139</v>
+      </c>
+      <c r="N23">
+        <v>734037.42254686437</v>
+      </c>
+      <c r="O23">
+        <v>722079.71614731045</v>
+      </c>
+      <c r="P23">
+        <v>758460.49917919911</v>
+      </c>
+      <c r="Q23">
+        <v>770975.09741565585</v>
+      </c>
+      <c r="R23">
+        <v>707854.62008530321</v>
+      </c>
+      <c r="S23">
+        <v>796627.17360064411</v>
+      </c>
+      <c r="T23">
+        <v>783649.85996618192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1174,8 +2044,44 @@
       <c r="H24">
         <v>702511.88920755731</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24">
+        <v>681321.64054193103</v>
+      </c>
+      <c r="J24">
+        <v>662228.95039803931</v>
+      </c>
+      <c r="K24">
+        <v>688302.26498836372</v>
+      </c>
+      <c r="L24">
+        <v>691818.77631330548</v>
+      </c>
+      <c r="M24">
+        <v>672438.26147890836</v>
+      </c>
+      <c r="N24">
+        <v>698904.63454584626</v>
+      </c>
+      <c r="O24">
+        <v>679329.83005023422</v>
+      </c>
+      <c r="P24">
+        <v>706061.52850716806</v>
+      </c>
+      <c r="Q24">
+        <v>709666.83614970383</v>
+      </c>
+      <c r="R24">
+        <v>642810.47642750526</v>
+      </c>
+      <c r="S24">
+        <v>716931.62118210422</v>
+      </c>
+      <c r="T24">
+        <v>696862.52834324003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -1200,8 +2106,44 @@
       <c r="H25">
         <v>178319.68510726746</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25">
+        <v>180252.57948783168</v>
+      </c>
+      <c r="J25">
+        <v>175310.17005026207</v>
+      </c>
+      <c r="K25">
+        <v>182059.61159719716</v>
+      </c>
+      <c r="L25">
+        <v>182969.90965518312</v>
+      </c>
+      <c r="M25">
+        <v>177952.99277754096</v>
+      </c>
+      <c r="N25">
+        <v>184804.1829994763</v>
+      </c>
+      <c r="O25">
+        <v>179736.97153013578</v>
+      </c>
+      <c r="P25">
+        <v>186656.84493404595</v>
+      </c>
+      <c r="Q25">
+        <v>187590.12915871618</v>
+      </c>
+      <c r="R25">
+        <v>170283.4269202023</v>
+      </c>
+      <c r="S25">
+        <v>189470.72020353223</v>
+      </c>
+      <c r="T25">
+        <v>184275.55529472567</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -1226,8 +2168,44 @@
       <c r="H26">
         <v>84430.786491773673</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26">
+        <v>87962.408213376388</v>
+      </c>
+      <c r="J26">
+        <v>85976.160285977589</v>
+      </c>
+      <c r="K26">
+        <v>89730.45261846525</v>
+      </c>
+      <c r="L26">
+        <v>90627.757144649921</v>
+      </c>
+      <c r="M26">
+        <v>88581.323918802998</v>
+      </c>
+      <c r="N26">
+        <v>92449.375063257394</v>
+      </c>
+      <c r="O26">
+        <v>90361.808529570917</v>
+      </c>
+      <c r="P26">
+        <v>94307.607502028855</v>
+      </c>
+      <c r="Q26">
+        <v>95250.683577049145</v>
+      </c>
+      <c r="R26">
+        <v>86893.204243837114</v>
+      </c>
+      <c r="S26">
+        <v>97165.222316947824</v>
+      </c>
+      <c r="T26">
+        <v>94971.168909790955</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -1252,8 +2230,44 @@
       <c r="H27">
         <v>127003.16976687804</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27">
+        <v>148951.53985236472</v>
+      </c>
+      <c r="J27">
+        <v>145588.11798473072</v>
+      </c>
+      <c r="K27">
+        <v>151945.46580339724</v>
+      </c>
+      <c r="L27">
+        <v>153464.92046143126</v>
+      </c>
+      <c r="M27">
+        <v>149999.58354778608</v>
+      </c>
+      <c r="N27">
+        <v>156549.56536270605</v>
+      </c>
+      <c r="O27">
+        <v>153014.57517709653</v>
+      </c>
+      <c r="P27">
+        <v>159696.2116264964</v>
+      </c>
+      <c r="Q27">
+        <v>161293.17374276137</v>
+      </c>
+      <c r="R27">
+        <v>147140.99849823525</v>
+      </c>
+      <c r="S27">
+        <v>164535.16653499086</v>
+      </c>
+      <c r="T27">
+        <v>160819.85632291049</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -1278,8 +2292,44 @@
       <c r="H28">
         <v>19827.405316636046</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28">
+        <v>17707.712700114265</v>
+      </c>
+      <c r="J28">
+        <v>17222.178642207899</v>
+      </c>
+      <c r="K28">
+        <v>17885.232519932906</v>
+      </c>
+      <c r="L28">
+        <v>17974.658682532568</v>
+      </c>
+      <c r="M28">
+        <v>17481.80513801151</v>
+      </c>
+      <c r="N28">
+        <v>18154.854635824951</v>
+      </c>
+      <c r="O28">
+        <v>17657.060234520071</v>
+      </c>
+      <c r="P28">
+        <v>18336.857053549091</v>
+      </c>
+      <c r="Q28">
+        <v>18428.541338816834</v>
+      </c>
+      <c r="R28">
+        <v>16728.359783042117</v>
+      </c>
+      <c r="S28">
+        <v>18613.287465738467</v>
+      </c>
+      <c r="T28">
+        <v>18102.923132000469</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -1304,8 +2354,44 @@
       <c r="H29">
         <v>131169.23599313098</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29">
+        <v>118969.26279422095</v>
+      </c>
+      <c r="J29">
+        <v>116282.86008596436</v>
+      </c>
+      <c r="K29">
+        <v>121360.54497638479</v>
+      </c>
+      <c r="L29">
+        <v>122574.15042614866</v>
+      </c>
+      <c r="M29">
+        <v>119806.34702942918</v>
+      </c>
+      <c r="N29">
+        <v>125037.89084971427</v>
+      </c>
+      <c r="O29">
+        <v>122214.45460472068</v>
+      </c>
+      <c r="P29">
+        <v>127551.1524557935</v>
+      </c>
+      <c r="Q29">
+        <v>128826.66398035144</v>
+      </c>
+      <c r="R29">
+        <v>117523.16314078512</v>
+      </c>
+      <c r="S29">
+        <v>131416.07992635647</v>
+      </c>
+      <c r="T29">
+        <v>128448.62005705168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -1330,8 +2416,44 @@
       <c r="H30">
         <v>37354.484531812406</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I30">
+        <v>40315.800738873098</v>
+      </c>
+      <c r="J30">
+        <v>39405.443947995329</v>
+      </c>
+      <c r="K30">
+        <v>41126.148333724443</v>
+      </c>
+      <c r="L30">
+        <v>41537.4098170617</v>
+      </c>
+      <c r="M30">
+        <v>40599.468305063543</v>
+      </c>
+      <c r="N30">
+        <v>42372.311754384646</v>
+      </c>
+      <c r="O30">
+        <v>41415.517617995312</v>
+      </c>
+      <c r="P30">
+        <v>43223.995220647768</v>
+      </c>
+      <c r="Q30">
+        <v>43656.235172854249</v>
+      </c>
+      <c r="R30">
+        <v>39825.752602848981</v>
+      </c>
+      <c r="S30">
+        <v>44533.725499828608</v>
+      </c>
+      <c r="T30">
+        <v>43528.125246606694</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -1356,8 +2478,44 @@
       <c r="H31">
         <v>39537.148605641414</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31">
+        <v>40212.017625393783</v>
+      </c>
+      <c r="J31">
+        <v>39304.004324175221</v>
+      </c>
+      <c r="K31">
+        <v>41020.279179664198</v>
+      </c>
+      <c r="L31">
+        <v>41430.481971460853</v>
+      </c>
+      <c r="M31">
+        <v>40494.954959202056</v>
+      </c>
+      <c r="N31">
+        <v>42263.234659087218</v>
+      </c>
+      <c r="O31">
+        <v>41308.90355388201</v>
+      </c>
+      <c r="P31">
+        <v>43112.725675734866</v>
+      </c>
+      <c r="Q31">
+        <v>43543.852932492213</v>
+      </c>
+      <c r="R31">
+        <v>39723.230997770326</v>
+      </c>
+      <c r="S31">
+        <v>44419.084376435298</v>
+      </c>
+      <c r="T31">
+        <v>43416.072793741609</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1382,8 +2540,45 @@
       <c r="H32">
         <v>22621.574279411743</v>
       </c>
+      <c r="I32">
+        <v>25046.755258435951</v>
+      </c>
+      <c r="J32">
+        <v>24481.18336550353</v>
+      </c>
+      <c r="K32">
+        <v>25550.195039130514</v>
+      </c>
+      <c r="L32">
+        <v>25805.696989521824</v>
+      </c>
+      <c r="M32">
+        <v>25222.987702661656</v>
+      </c>
+      <c r="N32">
+        <v>26324.391499011217</v>
+      </c>
+      <c r="O32">
+        <v>25729.969755485148</v>
+      </c>
+      <c r="P32">
+        <v>26853.511768141336</v>
+      </c>
+      <c r="Q32">
+        <v>27122.04688582275</v>
+      </c>
+      <c r="R32">
+        <v>24742.30599777637</v>
+      </c>
+      <c r="S32">
+        <v>27667.200028227784</v>
+      </c>
+      <c r="T32">
+        <v>27042.456801783937</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>